--- a/tests/testthat/_output_excel_snaps/create_table_of_contents.xlsx
+++ b/tests/testthat/_output_excel_snaps/create_table_of_contents.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13130" windowHeight="6110" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="6" state="visible" r:id="rId4"/>
